--- a/priorizacion_rice_sprint1.xlsx
+++ b/priorizacion_rice_sprint1.xlsx
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E13" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F13" s="61" t="n"/>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="E14" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F14" s="61" t="n"/>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="E15" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F15" s="61" t="n"/>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="E16" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F16" s="61" t="n"/>

--- a/priorizacion_rice_sprint1.xlsx
+++ b/priorizacion_rice_sprint1.xlsx
@@ -6575,7 +6575,7 @@
       </c>
       <c r="E17" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F17" s="61" t="n"/>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="E18" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F18" s="61" t="n"/>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="E19" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F19" s="61" t="n"/>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="E20" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F20" s="61" t="n"/>

--- a/priorizacion_rice_sprint1.xlsx
+++ b/priorizacion_rice_sprint1.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="E21" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F21" s="61" t="n"/>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="E22" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F22" s="61" t="n"/>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="E23" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F23" s="61" t="n"/>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="E24" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F24" s="61" t="n"/>

--- a/priorizacion_rice_sprint1.xlsx
+++ b/priorizacion_rice_sprint1.xlsx
@@ -6783,7 +6783,7 @@
       </c>
       <c r="E25" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F25" s="61" t="n"/>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="E26" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F26" s="61" t="n"/>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="E27" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F27" s="61" t="n"/>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="E28" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F28" s="61" t="n"/>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="E29" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F29" s="61" t="n"/>

--- a/priorizacion_rice_sprint1.xlsx
+++ b/priorizacion_rice_sprint1.xlsx
@@ -6913,7 +6913,7 @@
       </c>
       <c r="E30" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F30" s="61" t="n"/>
@@ -6939,7 +6939,7 @@
       </c>
       <c r="E31" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F31" s="61" t="n"/>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="E32" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F32" s="61" t="n"/>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="E33" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F33" s="61" t="n"/>

--- a/priorizacion_rice_sprint1.xlsx
+++ b/priorizacion_rice_sprint1.xlsx
@@ -7017,7 +7017,7 @@
       </c>
       <c r="E34" s="68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="F34" s="61" t="n"/>
